--- a/content/spreadsheets/Paycheck-Budget-Bill-Tracker.xlsx
+++ b/content/spreadsheets/Paycheck-Budget-Bill-Tracker.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -2957,7 +2956,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="84">
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A20:F20"/>
@@ -3814,7 +3812,6 @@
       <c r="F42" s="4" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="13">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A2:F2"/>
@@ -5128,7 +5125,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <autoFilter ref="A4:L34"/>
   <mergeCells count="4">
     <mergeCell ref="A3:L3"/>
@@ -5818,7 +5814,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <autoFilter ref="A4:G24"/>
   <mergeCells count="4">
     <mergeCell ref="A27:G27"/>
@@ -7226,7 +7221,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <autoFilter ref="A4:F104"/>
   <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
@@ -8376,7 +8370,6 @@
       <c r="H90" s="4" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="49">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B42:G42"/>
